--- a/F3M_Relacion_Inversores_assessment_ready_AI_v0.xlsx
+++ b/F3M_Relacion_Inversores_assessment_ready_AI_v0.xlsx
@@ -131,10 +131,10 @@
     <t>Gobierno integrado con Finanzas, Legal, Compliance, Comunicación, Secretaría General y Dirección, con workflow, evidencias y control de versiones.</t>
   </si>
   <si>
-    <t>Reporting regulatorio AI-enabled con generación asistida de borradores, validación de consistencia, alertas regulatorias y trazabilidad completa de revisión humana.</t>
-  </si>
-  <si>
-    <t>Generate draft regulatory filings; Draft sections of 10Q / 10K generation; Consolidate written financial reports into one compliant report</t>
+    <t>Reporting regulatorio basado en IA con generación asistida de borradores, validación de consistencia, alertas regulatorias y trazabilidad completa de revisión humana.</t>
+  </si>
+  <si>
+    <t>Generación de borradores de informes regulatorios; Generación de borradores de secciones de 10Q / 10K; Consolidación de informes financieros en un único informe conforme a normativa</t>
   </si>
   <si>
     <t>¿Existe calendario formal de reporting regulatorio?
@@ -167,10 +167,10 @@
     <t>Monitorización integrada con Legal, Compliance, RI y Finanzas, con alertas, owners, workflow de evaluación y reporting a governance.</t>
   </si>
   <si>
-    <t>AI monitoriza regulación global, sintetiza cambios, evalúa impacto preliminar y recomienda acciones de cumplimiento o comunicación.</t>
-  </si>
-  <si>
-    <t>Monitor emerging regulations and evaluate current state compliance; Global policy tracking; Summarizing legislative documents</t>
+    <t>IA monitoriza regulación global, sintetiza cambios, evalúa impacto preliminar y recomienda acciones de cumplimiento o comunicación.</t>
+  </si>
+  <si>
+    <t>Monitorización de la regulación emergente y evaluación del cumplimiento actual; Seguimiento de políticas globales; Resumen de documentos legislativos</t>
   </si>
   <si>
     <t>¿Se monitorizan cambios regulatorios?
@@ -203,10 +203,10 @@
     <t>Controles integrados con calendario financiero, comités, Legal/Compliance, canales de comunicación y gestión de insiders.</t>
   </si>
   <si>
-    <t>AI revisa consistencia entre comunicaciones, detecta posibles inconsistencias o riesgos de disclosure y recomienda validaciones previas.</t>
-  </si>
-  <si>
-    <t>Financial rules and regulations interpretations; Generate draft regulatory filings; AI-powered risk management and regulatory compliance</t>
+    <t>IA revisa consistencia entre comunicaciones, detecta posibles inconsistencias o riesgos de disclosure y recomienda validaciones previas.</t>
+  </si>
+  <si>
+    <t>Interpretación de normas y regulación financiera; Generación de borradores de informes regulatorios; Gestión de riesgos y cumplimiento regulatorio impulsados por IA</t>
   </si>
   <si>
     <t>¿Existen disclosure controls formalizados?
@@ -239,10 +239,10 @@
     <t>Coordinación integrada con CFO, CEO, Consejo/Comisiones, Legal, Comunicación, Auditoría y Finanzas, con trazabilidad de decisiones.</t>
   </si>
   <si>
-    <t>AI sintetiza inputs internos, identifica inconsistencias, prepara briefs ejecutivos y facilita la alineación de mensajes antes de interacciones externas.</t>
-  </si>
-  <si>
-    <t>Generate executive level overview of company financial health; FinanceAI Insights Platform; Consolidate written financial reports into one compliant report</t>
+    <t>IA sintetiza inputs internos, identifica inconsistencias, prepara briefs ejecutivos y facilita la alineación de mensajes antes de interacciones externas.</t>
+  </si>
+  <si>
+    <t>Generación de una visión ejecutiva de la salud financiera de la compañía; FinanceAI Insights Platform; Consolidación de informes financieros en un único informe conforme a normativa</t>
   </si>
   <si>
     <t>¿Existen foros de coordinación de RI?
@@ -278,10 +278,10 @@
     <t>Estrategia integrada con plan corporativo, capital allocation, performance, ESG, feedback inversor y análisis competitivo.</t>
   </si>
   <si>
-    <t>AI analiza mercado, feedback, preguntas de inversores y tendencias para ajustar equity story, mensajes y prioridades de engagement.</t>
-  </si>
-  <si>
-    <t>Marketing content assistant; Next-level market intelligence; Generate executive level overview of company financial health</t>
+    <t>IA analiza mercado, feedback, preguntas de inversores y tendencias para ajustar equity story, mensajes y prioridades de engagement.</t>
+  </si>
+  <si>
+    <t>Asistente de contenidos de marketing; Inteligencia de mercado de nueva generación; Generación de una visión ejecutiva de la salud financiera de la compañía</t>
   </si>
   <si>
     <t>¿Existe estrategia de RI documentada?
@@ -314,10 +314,10 @@
     <t>Plan integrado con reporting financiero, estrategia, comunicación, agenda ejecutiva, targeting de inversores y feedback post-evento.</t>
   </si>
   <si>
-    <t>AI genera briefs, Q&amp;A, resúmenes de feedback, propuestas de mensajes y materiales base para eventos y comunicaciones financieras.</t>
-  </si>
-  <si>
-    <t>Marketing content assistant; Generate executive level overview of company financial health; Consolidate written financial reports into one compliant report</t>
+    <t>IA genera briefs, Q&amp;A, resúmenes de feedback, propuestas de mensajes y materiales base para eventos y comunicaciones financieras.</t>
+  </si>
+  <si>
+    <t>Asistente de contenidos de marketing; Generación de una visión ejecutiva de la salud financiera de la compañía; Consolidación de informes financieros en un único informe conforme a normativa</t>
   </si>
   <si>
     <t>¿Existe calendario anual de RI?
@@ -350,10 +350,10 @@
     <t>Gestión integrada con targeting, mensajes, calendario, percepción del mercado, análisis de preguntas y acciones de mejora.</t>
   </si>
   <si>
-    <t>AI sintetiza feedback de inversores/analistas, identifica temas recurrentes, riesgos de percepción y recomendaciones de engagement.</t>
-  </si>
-  <si>
-    <t>FinanceAI Insights Platform; Smarter intelligence; Enterprise-wide data search and access</t>
+    <t>IA sintetiza feedback de inversores/analistas, identifica temas recurrentes, riesgos de percepción y recomendaciones de engagement.</t>
+  </si>
+  <si>
+    <t>FinanceAI Insights Platform; Inteligencia más avanzada; Búsqueda y acceso a datos en toda la compañía</t>
   </si>
   <si>
     <t>¿Existe CRM/tracker de inversores?
@@ -386,10 +386,10 @@
     <t>Modelo integrado de performance RI con objetivos, benchmarking, percepción de mercado, análisis de analistas y mejora continua.</t>
   </si>
   <si>
-    <t>AI identifica relaciones entre actividad RI, percepción de mercado, narrativa, preguntas y recomendaciones para mejorar efectividad.</t>
-  </si>
-  <si>
-    <t>Next-level market intelligence; FinanceAI Insights Platform; Generate executive level overview of company financial health</t>
+    <t>IA identifica relaciones entre actividad RI, percepción de mercado, narrativa, preguntas y recomendaciones para mejorar efectividad.</t>
+  </si>
+  <si>
+    <t>Inteligencia de mercado de nueva generación; FinanceAI Insights Platform; Generación de una visión ejecutiva de la salud financiera de la compañía</t>
   </si>
   <si>
     <t>¿Existen KPIs de RI?
@@ -425,10 +425,10 @@
     <t>Análisis integrado con equity story, capital allocation, performance, riesgos, feedback inversor y decisiones de comunicación.</t>
   </si>
   <si>
-    <t>AI analiza datos financieros y de mercado, predice valoración relativa, identifica drivers y recomienda focos de comunicación o acción.</t>
-  </si>
-  <si>
-    <t>Predictive company valuation analyzing financial data; Generate investing strategies; Next-level market intelligence</t>
+    <t>IA analiza datos financieros y de mercado, predice valoración relativa, identifica drivers y recomienda focos de comunicación o acción.</t>
+  </si>
+  <si>
+    <t>Valoración predictiva de la compañía a partir del análisis de datos financieros; Generación de estrategias de inversión; Inteligencia de mercado de nueva generación</t>
   </si>
   <si>
     <t>¿Se analiza valoración y múltiplos frente a peers?
@@ -461,10 +461,10 @@
     <t>Coordinación integrada con estrategia de financiación, capital markets, bancos, rating, comunicación, legal y dirección.</t>
   </si>
   <si>
-    <t>AI sintetiza información financiera, mercado y riesgos, prepara materiales base y recomienda mensajes según operación y audiencia.</t>
-  </si>
-  <si>
-    <t>Generate investing strategies; Research-based report generation / KYC; Generate executive level overview of company financial health</t>
+    <t>IA sintetiza información financiera, mercado y riesgos, prepara materiales base y recomienda mensajes según operación y audiencia.</t>
+  </si>
+  <si>
+    <t>Generación de estrategias de inversión; Generación de informes de investigación / KYC; Generación de una visión ejecutiva de la salud financiera de la compañía</t>
   </si>
   <si>
     <t>¿Está definido el rol de RI en operaciones de mercado?
@@ -497,10 +497,10 @@
     <t>Gestión integrada con forecast interno, planificación, performance, equity story y preparación de resultados/Q&amp;A.</t>
   </si>
   <si>
-    <t>AI compara consensus vs forecast, identifica gaps de expectativa, explica drivers y recomienda puntos de comunicación preventiva.</t>
-  </si>
-  <si>
-    <t>Generate executive level overview of company financial health; FinanceAI Insights Platform; Identify past data patterns to predict and improve future financial performance</t>
+    <t>IA compara consensus vs forecast, identifica gaps de expectativa, explica drivers y recomienda puntos de comunicación preventiva.</t>
+  </si>
+  <si>
+    <t>Generación de una visión ejecutiva de la salud financiera de la compañía; FinanceAI Insights Platform; Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro</t>
   </si>
   <si>
     <t>¿Se monitoriza consensus de analistas?
@@ -533,10 +533,10 @@
     <t>Reporting integrado con estrategia, capital allocation, financiación, comunicación, riesgos y decisiones del comité/directorio.</t>
   </si>
   <si>
-    <t>AI genera overview ejecutivo del mercado de capitales, resume feedback, identifica riesgos/oportunidades y recomienda acciones estratégicas.</t>
-  </si>
-  <si>
-    <t>Generate executive level overview of company financial health; Next-level market intelligence; FinanceAI Insights Platform</t>
+    <t>IA genera overview ejecutivo del mercado de capitales, resume feedback, identifica riesgos/oportunidades y recomienda acciones estratégicas.</t>
+  </si>
+  <si>
+    <t>Generación de una visión ejecutiva de la salud financiera de la compañía; Inteligencia de mercado de nueva generación; FinanceAI Insights Platform</t>
   </si>
   <si>
     <t>¿Existe reporting RI para dirección?

--- a/F3M_Relacion_Inversores_assessment_ready_AI_v0.xlsx
+++ b/F3M_Relacion_Inversores_assessment_ready_AI_v0.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="222">
   <si>
     <t>Capacidad</t>
   </si>
@@ -724,6 +724,42 @@
   </si>
   <si>
     <t>Evaluar situación actual, sustentar el score con evidencias, separar las tres palancas y validar resultados con Finanzas, Legal, Comunicación, Compliance y responsables de RI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borrador de informes regulatorios; Borrador de secciones 10Q y 10K; Consolidación de informes en un único documento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vigilancia de regulación emergente; Seguimiento de políticas y regulación global; Resumen de documentos legislativos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpretación de normativa financiera; Borrador de informes regulatorios; Vigilancia continua de riesgo y cumplimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visión ejecutiva de la salud financiera; Analista digital de Finanzas bajo demanda; Consolidación de informes en un único documento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asistente de contenidos de comunicación; Inteligencia de mercado; Visión ejecutiva de la salud financiera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asistente de contenidos de comunicación; Visión ejecutiva de la salud financiera; Consolidación de informes en un único documento; Generación de contenido para el earnings call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analista digital de Finanzas bajo demanda; Síntesis multifuente para informes de análisis; Consulta del dato en lenguaje natural</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inteligencia de mercado; Analista digital de Finanzas bajo demanda; Visión ejecutiva de la salud financiera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valoración predictiva de la compañía; Generación de estrategias de inversión; Inteligencia de mercado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación de estrategias de inversión; Informes de investigación y KYC; Visión ejecutiva de la salud financiera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visión ejecutiva de la salud financiera; Analista digital de Finanzas bajo demanda; Patrones históricos para predecir el rendimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visión ejecutiva de la salud financiera; Inteligencia de mercado; Analista digital de Finanzas bajo demanda</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1503,7 @@
         <v>27</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -1525,7 +1561,7 @@
         <v>38</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>39</v>
+        <v>211</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -1583,7 +1619,7 @@
         <v>49</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1641,7 +1677,7 @@
         <v>60</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1699,7 +1735,7 @@
         <v>72</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1757,7 +1793,7 @@
         <v>83</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1815,7 +1851,7 @@
         <v>94</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1873,7 +1909,7 @@
         <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>106</v>
+        <v>217</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -1931,7 +1967,7 @@
         <v>117</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>118</v>
+        <v>218</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -1989,7 +2025,7 @@
         <v>128</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2047,7 +2083,7 @@
         <v>139</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2105,7 +2141,7 @@
         <v>150</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -2849,7 +2885,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="G2" s="2" t="str">
         <f t="shared" ref="G2:G13" si="0">IF(C2="","",IF(C2&gt;=3,"Oleada 1",IF(C2=2,"Oleada 2",IF(C2=1,"Oleada 3",""))))</f>
@@ -2880,7 +2916,7 @@
         <v>42</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>211</v>
       </c>
       <c r="G3" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2911,7 +2947,7 @@
         <v>53</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="G4" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2942,7 +2978,7 @@
         <v>64</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="G5" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2973,7 +3009,7 @@
         <v>76</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="G6" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3004,7 +3040,7 @@
         <v>87</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="G7" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3035,7 +3071,7 @@
         <v>98</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="G8" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3066,7 +3102,7 @@
         <v>109</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>106</v>
+        <v>217</v>
       </c>
       <c r="G9" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3097,7 +3133,7 @@
         <v>121</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>118</v>
+        <v>218</v>
       </c>
       <c r="G10" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3128,7 +3164,7 @@
         <v>132</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="G11" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3159,7 +3195,7 @@
         <v>143</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="G12" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3190,7 +3226,7 @@
         <v>154</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="G13" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3250,7 +3286,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>27</v>
@@ -3267,7 +3303,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>39</v>
+        <v>211</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>38</v>
@@ -3284,7 +3320,7 @@
         <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>49</v>
@@ -3301,7 +3337,7 @@
         <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>60</v>
@@ -3318,7 +3354,7 @@
         <v>66</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>72</v>
@@ -3335,7 +3371,7 @@
         <v>77</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>83</v>
@@ -3352,7 +3388,7 @@
         <v>88</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>94</v>
@@ -3369,7 +3405,7 @@
         <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>106</v>
+        <v>217</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>105</v>
@@ -3386,7 +3422,7 @@
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>118</v>
+        <v>218</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>117</v>
@@ -3403,7 +3439,7 @@
         <v>122</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>128</v>
@@ -3420,7 +3456,7 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>139</v>
@@ -3437,7 +3473,7 @@
         <v>144</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>150</v>

--- a/F3M_Relacion_Inversores_assessment_ready_AI_v0.xlsx
+++ b/F3M_Relacion_Inversores_assessment_ready_AI_v0.xlsx
@@ -131,7 +131,7 @@
     <t>Gobierno integrado con Finanzas, Legal, Compliance, Comunicación, Secretaría General y Dirección, con workflow, evidencias y control de versiones.</t>
   </si>
   <si>
-    <t>Reporting regulatorio basado en IA con generación asistida de borradores, validación de consistencia, alertas regulatorias y trazabilidad completa de revisión humana.</t>
+    <t>Informes regulatorios basados en IA, con generación asistida de borradores, validación de consistencia, alertas regulatorias y trazabilidad completa de la revisión humana.</t>
   </si>
   <si>
     <t>Generación de borradores de informes regulatorios; Generación de borradores de secciones de 10Q / 10K; Consolidación de informes financieros en un único informe conforme a normativa</t>
@@ -203,7 +203,7 @@
     <t>Controles integrados con calendario financiero, comités, Legal/Compliance, canales de comunicación y gestión de insiders.</t>
   </si>
   <si>
-    <t>IA revisa consistencia entre comunicaciones, detecta posibles inconsistencias o riesgos de disclosure y recomienda validaciones previas.</t>
+    <t>IA revisa consistencia entre comunicaciones, detecta posibles inconsistencias o riesgos de información al mercado y recomienda validaciones previas.</t>
   </si>
   <si>
     <t>Interpretación de normas y regulación financiera; Generación de borradores de informes regulatorios; Gestión de riesgos y cumplimiento regulatorio impulsados por IA</t>
@@ -239,7 +239,7 @@
     <t>Coordinación integrada con CFO, CEO, Consejo/Comisiones, Legal, Comunicación, Auditoría y Finanzas, con trazabilidad de decisiones.</t>
   </si>
   <si>
-    <t>IA sintetiza inputs internos, identifica inconsistencias, prepara briefs ejecutivos y facilita la alineación de mensajes antes de interacciones externas.</t>
+    <t>La IA sintetiza las aportaciones internas, identifica inconsistencias, prepara notas informativas para dirección y facilita alinear los mensajes antes de las interacciones externas.</t>
   </si>
   <si>
     <t>Generación de una visión ejecutiva de la salud financiera de la compañía; FinanceAI Insights Platform; Consolidación de informes financieros en un único informe conforme a normativa</t>
@@ -278,7 +278,7 @@
     <t>Estrategia integrada con plan corporativo, capital allocation, performance, ESG, feedback inversor y análisis competitivo.</t>
   </si>
   <si>
-    <t>IA analiza mercado, feedback, preguntas de inversores y tendencias para ajustar equity story, mensajes y prioridades de engagement.</t>
+    <t>La IA analiza mercado, comentarios, preguntas de inversores y tendencias para ajustar el relato de inversión, los mensajes y las prioridades de relación.</t>
   </si>
   <si>
     <t>Asistente de contenidos de marketing; Inteligencia de mercado de nueva generación; Generación de una visión ejecutiva de la salud financiera de la compañía</t>
@@ -314,7 +314,7 @@
     <t>Plan integrado con reporting financiero, estrategia, comunicación, agenda ejecutiva, targeting de inversores y feedback post-evento.</t>
   </si>
   <si>
-    <t>IA genera briefs, Q&amp;A, resúmenes de feedback, propuestas de mensajes y materiales base para eventos y comunicaciones financieras.</t>
+    <t>IA genera notas informativas, Q&amp;A, resúmenes de comentarios, propuestas de mensajes y materiales base para eventos y comunicaciones financieras.</t>
   </si>
   <si>
     <t>Asistente de contenidos de marketing; Generación de una visión ejecutiva de la salud financiera de la compañía; Consolidación de informes financieros en un único informe conforme a normativa</t>
@@ -350,7 +350,7 @@
     <t>Gestión integrada con targeting, mensajes, calendario, percepción del mercado, análisis de preguntas y acciones de mejora.</t>
   </si>
   <si>
-    <t>IA sintetiza feedback de inversores/analistas, identifica temas recurrentes, riesgos de percepción y recomendaciones de engagement.</t>
+    <t>IA sintetiza comentarios de inversores/analistas, identifica temas recurrentes, riesgos de percepción y recomendaciones de relación con el inversor.</t>
   </si>
   <si>
     <t>FinanceAI Insights Platform; Inteligencia más avanzada; Búsqueda y acceso a datos en toda la compañía</t>
@@ -497,7 +497,7 @@
     <t>Gestión integrada con forecast interno, planificación, performance, equity story y preparación de resultados/Q&amp;A.</t>
   </si>
   <si>
-    <t>IA compara consensus vs forecast, identifica gaps de expectativa, explica drivers y recomienda puntos de comunicación preventiva.</t>
+    <t>La IA compara el consenso de mercado con la previsión propia, identifica las brechas de expectativa, explica los drivers y recomienda los puntos de comunicación preventiva.</t>
   </si>
   <si>
     <t>Generación de una visión ejecutiva de la salud financiera de la compañía; FinanceAI Insights Platform; Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro</t>
@@ -533,7 +533,7 @@
     <t>Reporting integrado con estrategia, capital allocation, financiación, comunicación, riesgos y decisiones del comité/directorio.</t>
   </si>
   <si>
-    <t>IA genera overview ejecutivo del mercado de capitales, resume feedback, identifica riesgos/oportunidades y recomienda acciones estratégicas.</t>
+    <t>IA genera panorámica ejecutiva del mercado de capitales, resume comentarios, identifica riesgos/oportunidades y recomienda acciones estratégicas.</t>
   </si>
   <si>
     <t>Generación de una visión ejecutiva de la salud financiera de la compañía; Inteligencia de mercado de nueva generación; FinanceAI Insights Platform</t>

--- a/F3M_Relacion_Inversores_assessment_ready_AI_v0.xlsx
+++ b/F3M_Relacion_Inversores_assessment_ready_AI_v0.xlsx
@@ -146,7 +146,7 @@
     <t>Calendario regulatorio; matriz RACI; filings; aprobaciones; evidencias de revisión; control de versiones; actas de comité.</t>
   </si>
   <si>
-    <t>Diseñar modelo de gobierno de reporting regulatorio con calendario, RACI, workflow de revisión, control de versiones y evidencias de aprobación.</t>
+    <t>Diseñar modelo de gobierno de la información regulatoria con calendario, RACI, flujo de revisión, control de versiones y evidencias de aprobación.</t>
   </si>
   <si>
     <t>1.2 Monitorización normativa y cumplimiento de obligaciones de mercado</t>
@@ -182,7 +182,7 @@
     <t>Matriz de obligaciones; alertas regulatorias; análisis de impacto; actas de seguimiento; políticas actualizadas; evidencias de acciones.</t>
   </si>
   <si>
-    <t>Implantar regulatory intelligence para RI con matriz de obligaciones, alertas, análisis de impacto, owners y seguimiento de acciones.</t>
+    <t>Implantar vigilancia regulatoria para RI con matriz de obligaciones, alertas, análisis de impacto, responsables y seguimiento de acciones.</t>
   </si>
   <si>
     <t>1.3 Gobierno de información privilegiada, consistencia y disclosure controls</t>
@@ -218,7 +218,7 @@
     <t>Política de disclosure; insider lists; versionado; aprobaciones; actas; comunicaciones externas; checklist de revisión.</t>
   </si>
   <si>
-    <t>Formalizar controles de disclosure con criterios de materialidad, workflow, revisión de consistencia, evidencias y gestión de información sensible.</t>
+    <t>Formalizar controles de difusión de información con criterios de materialidad, flujo de trabajo, revisión de consistencia, evidencias y gestión de información sensible.</t>
   </si>
   <si>
     <t>1.4 Coordinación con órganos de gobierno, auditoría y stakeholders internos</t>
@@ -254,7 +254,7 @@
     <t>Calendario de comités; actas; briefing books; versiones de mensajes; aprobaciones; inputs de áreas; documentación del Consejo.</t>
   </si>
   <si>
-    <t>Crear rutina de coordinación de RI con stakeholders internos, agenda, inputs, decisiones, mensajes clave y trazabilidad de aprobaciones.</t>
+    <t>Crear rutina de coordinación de RI con interlocutores internos, agenda, aportaciones, decisiones, mensajes clave y trazabilidad de aprobaciones.</t>
   </si>
   <si>
     <t>Planificación y estrategia de RI</t>
@@ -293,7 +293,7 @@
     <t>Plan RI; equity story; investor targeting; calendario; KPIs; feedback de inversores; presentaciones; análisis de percepción.</t>
   </si>
   <si>
-    <t>Definir estrategia de RI con equity story, segmentación de inversores, mensajes clave, calendario, KPIs y mecanismo de feedback.</t>
+    <t>Definir estrategia de RI con argumentario de inversión (equity story), segmentación de inversores, mensajes clave, calendario, KPIs y recogida de opiniones.</t>
   </si>
   <si>
     <t>2.2 Calendario de comunicación financiera y eventos con mercado</t>
@@ -329,7 +329,7 @@
     <t>Calendario RI; earnings materials; Q&amp;A; roadshow tracker; investor day materials; feedback logs; approvals; follow-up actions.</t>
   </si>
   <si>
-    <t>Implantar modelo de planificación de eventos RI con calendario, materiales, Q&amp;A, approvals, feedback y seguimiento de acciones.</t>
+    <t>Implantar modelo de planificación de eventos de RI con calendario, materiales, preguntas y respuestas, aprobaciones, opiniones y seguimiento de acciones.</t>
   </si>
   <si>
     <t>2.3 Gestión de inversores, analistas y feedback del mercado</t>
@@ -365,7 +365,7 @@
     <t>CRM RI; logs de reuniones; feedback de inversores; informes de analistas; Q&amp;A; trackers de acciones; segmentación.</t>
   </si>
   <si>
-    <t>Crear modelo de investor intelligence con CRM, feedback estructurado, análisis de temas, percepción, acciones y reporting ejecutivo.</t>
+    <t>Crear modelo de inteligencia de inversores con CRM, opiniones estructuradas, análisis de temas, percepción, acciones e informes a la dirección.</t>
   </si>
   <si>
     <t>2.4 Métricas de efectividad, percepción y mejora continua de RI</t>
@@ -401,7 +401,7 @@
     <t>Dashboard RI; encuestas de percepción; coverage de analistas; feedback; benchmarking; KPIs de actividad; acciones de mejora.</t>
   </si>
   <si>
-    <t>Implantar scorecard de RI con KPIs de actividad, percepción, cobertura, feedback, benchmarking y mejora continua.</t>
+    <t>Implantar cuadro de mando de RI con KPIs de actividad, percepción, cobertura, opiniones, comparación con referentes y mejora continua.</t>
   </si>
   <si>
     <t>Financiación y valoración de mercados de capitales</t>
@@ -440,7 +440,7 @@
     <t>Modelo de valoración; comparables; consensus; informes de analistas; evolución de múltiplos; presentaciones; análisis de sensibilidad.</t>
   </si>
   <si>
-    <t>Crear modelo de valoración y percepción de mercado con peers, consensus, drivers, sensibilidad y recomendaciones de comunicación.</t>
+    <t>Crear modelo de valoración y percepción de mercado con comparables, consenso de analistas, drivers, sensibilidad y recomendaciones de comunicación.</t>
   </si>
   <si>
     <t>3.2 Soporte financiero a operaciones de mercado y financiación corporativa</t>
@@ -476,7 +476,7 @@
     <t>Deal materials; Q&amp;A; calendario de operación; actas; feedback de bancos/inversores; approvals; documentación financiera.</t>
   </si>
   <si>
-    <t>Definir playbook de RI para operaciones de mercado con roles, materiales, Q&amp;A, approvals, feedback y coordinación con stakeholders.</t>
+    <t>Definir guía de actuación de RI para operaciones de mercado con roles, materiales, preguntas y respuestas, aprobaciones, opiniones y coordinación con las partes implicadas.</t>
   </si>
   <si>
     <t>3.3 Gestión de consensus, guidance y expectativas del mercado</t>
@@ -512,7 +512,7 @@
     <t>Consensus tracker; guidance; forecast interno; informes de analistas; Q&amp;A; earnings prep; análisis de gaps.</t>
   </si>
   <si>
-    <t>Implantar modelo de consensus management con tracker de analistas, comparación con forecast, gaps de expectativa y recomendaciones de mensajes.</t>
+    <t>Implantar gestión del consenso de analistas con seguimiento por analista, comparación con la previsión, diferencias de expectativas y recomendaciones de mensajes.</t>
   </si>
   <si>
     <t>3.4 Reporting estratégico a dirección sobre mercado, inversores y capital</t>
@@ -548,7 +548,7 @@
     <t>Pack ejecutivo RI; actas de comité; análisis de mercado; feedback inversor; coverage de analistas; recomendaciones; decisiones.</t>
   </si>
   <si>
-    <t>Crear pack ejecutivo de RI/capital markets con valoración, consensus, feedback, riesgos, oportunidades y recomendaciones de acción.</t>
+    <t>Crear informe ejecutivo de RI y mercados de capitales con valoración, consenso, opiniones, riesgos, oportunidades y recomendaciones de acción.</t>
   </si>
   <si>
     <t>Score global dominio</t>
